--- a/PTBR/Lang/PTBR/Dialog/Drama/ineien.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/ineien.xlsx
@@ -413,11 +413,10 @@
 Feel free to use my archives If you have something you would like to look up. However, it would be wise to ask Meister Lemixes directly, when he is in a good mood.</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Bem-vindo ao meu refúgio. Ouvi falar de você por Ashland. Não podemos oferecer muita hospitalidade, mas espero que tire um tempo para relaxar._x000D_
-_x000D_
-Sinta-se à vontade para usar meus arquivos se houver algo que queira consultar. No entanto, seria prudente perguntar diretamente ao Meister Lemixes quando ele estiver de bom humor.</t>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Bem-vindo ao meu forte. Fiquei sabendo de você pelo Ashland. Não podemos oferecer muita hospitalidade, mas espero que tire um tempo para descansar.
+Fique à vontade para usar meus arquivos se tiver algo que queira consultar. Porém, seria sensato perguntar diretamente ao Mestre Lemixes, quando ele estiver de bom humor.</t>
         </is>
       </c>
     </row>
@@ -445,7 +444,7 @@
           <t>I have some questions.</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t>Tenho algumas perguntas.</t>
         </is>
@@ -506,9 +505,9 @@
           <t>How may I help?</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Como posso ajudar?  </t>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Como posso ajudar?</t>
         </is>
       </c>
     </row>
@@ -536,9 +535,9 @@
           <t>Tell me about Willow.</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fale-me sobre Willow.  </t>
+      <c r="K21" s="4" t="inlineStr">
+        <is>
+          <t>Fale-me de Salgueiro.</t>
         </is>
       </c>
     </row>
@@ -566,9 +565,9 @@
           <t>(Back)</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(Voltar)  </t>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>(Voltar)</t>
         </is>
       </c>
     </row>
@@ -605,9 +604,9 @@
           <t>Willow is a fort in the territory of Mysilia. 150 years ago when I was given this land, I named it Lothria. It means "Promised Land" in the old Elean language. But for some time now, people have called the fort by the name of the willow trees that surround it. Now I call it Willow, too.</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Willow é um forte no território de Mysilia. Há 150 anos, quando recebi estas terras, dei a elas o nome de Lothria. Significa "Terra Prometida" no antigo idioma Elean. Mas, há algum tempo, as pessoas começaram a chamar o forte pelo nome dos salgueiros que o cercam. Agora, eu também o chamo de Willow.  </t>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Salgueiro é um forte no território de Mysilia. Há 150 anos, quando recebi esta terra, a chamei de Lothria. Significa "Terra Prometida" no antigo idioma Elea. Mas já faz um tempo que o povo chama o forte pelo nome dos salgueiros que o cercam. Hoje eu também o chamo de Salgueiro.</t>
         </is>
       </c>
     </row>
@@ -625,9 +624,9 @@
           <t>...In the past, Willow was the symbol of the coexistence of humans and Elea that Mysilia upheld. However, when the last war caused the relationship between the two races to be strained, Willow's light has also lost its place to shine and has been smoldering since then.</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...No passado, Willow era o símbolo da coexistência entre humanos e Elea, um ideal defendido por Mysilia. No entanto, quando a última guerra tensionou a relação entre as duas raças, a luz de Willow também perdeu seu lugar para brilhar e, desde então, tem apenas fumegado.  </t>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>...No passado, Salgueiro era o símbolo da convivência de humanos e Elea que Mysilia defendia. Porém, quando a última guerra esticou a relação entre as duas raças, a luz de Salgueiro também perdeu onde brilhar e vem fumegando desde então.</t>
         </is>
       </c>
     </row>
